--- a/data/dividends_info_20260817.xlsx
+++ b/data/dividends_info_20260817.xlsx
@@ -523,10 +523,10 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>48.20000076293945</v>
+        <v>49.06000137329102</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1867219887456935</v>
+        <v>0.1834488330222455</v>
       </c>
       <c r="J2" t="n">
         <v>210</v>
@@ -570,10 +570,10 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>67.25</v>
+        <v>66.84999847412109</v>
       </c>
       <c r="I3" t="n">
-        <v>1.04089219330855</v>
+        <v>1.047120442749125</v>
       </c>
       <c r="J3" t="n">
         <v>189</v>
@@ -617,10 +617,10 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>9.460000038146973</v>
+        <v>9.300000190734863</v>
       </c>
       <c r="I4" t="n">
-        <v>0.6342494689011948</v>
+        <v>0.6451612770908873</v>
       </c>
       <c r="J4" t="n">
         <v>119</v>
@@ -664,10 +664,10 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>0.4979999959468842</v>
+        <v>0.4659999907016754</v>
       </c>
       <c r="I5" t="n">
-        <v>0.8032128579428007</v>
+        <v>0.8583691158399027</v>
       </c>
       <c r="J5" t="n">
         <v>119</v>
@@ -711,10 +711,10 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>48.20000076293945</v>
+        <v>49.06000137329102</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1867219887456935</v>
+        <v>0.1834488330222455</v>
       </c>
       <c r="J6" t="n">
         <v>119</v>
@@ -758,10 +758,10 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>2.125</v>
+        <v>2.115000009536743</v>
       </c>
       <c r="I7" t="n">
-        <v>3.623529411764706</v>
+        <v>3.640661922118176</v>
       </c>
       <c r="J7" t="n">
         <v>98</v>
@@ -805,10 +805,10 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>23.68000030517578</v>
+        <v>23.77499961853027</v>
       </c>
       <c r="I8" t="n">
-        <v>1.140202688008351</v>
+        <v>1.135646705918605</v>
       </c>
       <c r="J8" t="n">
         <v>98</v>
@@ -852,10 +852,10 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>23.20000076293945</v>
+        <v>22.95999908447266</v>
       </c>
       <c r="I9" t="n">
-        <v>2.543103364645091</v>
+        <v>2.569686513615778</v>
       </c>
       <c r="J9" t="n">
         <v>98</v>
@@ -899,10 +899,10 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>5.840000152587891</v>
+        <v>5.809999942779541</v>
       </c>
       <c r="I10" t="n">
-        <v>3.424657444766908</v>
+        <v>3.442340825640675</v>
       </c>
       <c r="J10" t="n">
         <v>91</v>
@@ -993,10 +993,10 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>7.5</v>
+        <v>7.449999809265137</v>
       </c>
       <c r="I12" t="n">
-        <v>0.8</v>
+        <v>0.8053691481358354</v>
       </c>
       <c r="J12" t="n">
         <v>63</v>
@@ -1040,10 +1040,10 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>0.4979999959468842</v>
+        <v>0.4659999907016754</v>
       </c>
       <c r="I13" t="n">
-        <v>0.8032128579428007</v>
+        <v>0.8583691158399027</v>
       </c>
       <c r="J13" t="n">
         <v>63</v>
@@ -1134,10 +1134,10 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>5.059999942779541</v>
+        <v>5.079999923706055</v>
       </c>
       <c r="I15" t="n">
-        <v>0.7509881507849578</v>
+        <v>0.7480315072972982</v>
       </c>
       <c r="J15" t="n">
         <v>42</v>
@@ -1181,10 +1181,10 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>23.68499946594238</v>
+        <v>23.77499961853027</v>
       </c>
       <c r="I16" t="n">
-        <v>1.139962026970885</v>
+        <v>1.135646705918605</v>
       </c>
       <c r="J16" t="n">
         <v>35</v>
@@ -1228,10 +1228,10 @@
         </is>
       </c>
       <c r="H17" t="n">
-        <v>1.973999977111816</v>
+        <v>1.950000047683716</v>
       </c>
       <c r="I17" t="n">
-        <v>2.88753802740147</v>
+        <v>2.923076851598377</v>
       </c>
       <c r="J17" t="n">
         <v>35</v>
@@ -1275,10 +1275,10 @@
         </is>
       </c>
       <c r="H18" t="n">
-        <v>48.20000076293945</v>
+        <v>49.06000137329102</v>
       </c>
       <c r="I18" t="n">
-        <v>0.1867219887456935</v>
+        <v>0.1834488330222455</v>
       </c>
       <c r="J18" t="n">
         <v>35</v>
@@ -1322,10 +1322,10 @@
         </is>
       </c>
       <c r="H19" t="n">
-        <v>94.59999847412109</v>
+        <v>92.25</v>
       </c>
       <c r="I19" t="n">
-        <v>1.405919684410816</v>
+        <v>1.441734417344174</v>
       </c>
       <c r="J19" t="n">
         <v>35</v>
@@ -1369,10 +1369,10 @@
         </is>
       </c>
       <c r="H20" t="n">
-        <v>5.800000190734863</v>
+        <v>5.739999771118164</v>
       </c>
       <c r="I20" t="n">
-        <v>5.172413623006964</v>
+        <v>5.226481044642261</v>
       </c>
       <c r="J20" t="n">
         <v>28</v>
@@ -1416,10 +1416,10 @@
         </is>
       </c>
       <c r="H21" t="n">
-        <v>0.4979999959468842</v>
+        <v>0.4659999907016754</v>
       </c>
       <c r="I21" t="n">
-        <v>0.8032128579428007</v>
+        <v>0.8583691158399027</v>
       </c>
       <c r="J21" t="n">
         <v>7</v>
@@ -1463,10 +1463,10 @@
         </is>
       </c>
       <c r="H22" t="n">
-        <v>2.5</v>
+        <v>2.440000057220459</v>
       </c>
       <c r="I22" t="n">
-        <v>8.799999999999999</v>
+        <v>9.016393231179443</v>
       </c>
       <c r="J22" t="n">
         <v>-7</v>
@@ -1510,10 +1510,10 @@
         </is>
       </c>
       <c r="H23" t="n">
-        <v>5.059999942779541</v>
+        <v>5.079999923706055</v>
       </c>
       <c r="I23" t="n">
-        <v>0.7509881507849578</v>
+        <v>0.7480315072972982</v>
       </c>
       <c r="J23" t="n">
         <v>-14</v>
@@ -1604,10 +1604,10 @@
         </is>
       </c>
       <c r="H25" t="n">
-        <v>2.599999904632568</v>
+        <v>2.539999961853027</v>
       </c>
       <c r="I25" t="n">
-        <v>5.69111559336426</v>
+        <v>5.825551268593363</v>
       </c>
       <c r="J25" t="n">
         <v>-14</v>
@@ -1651,10 +1651,10 @@
         </is>
       </c>
       <c r="H26" t="n">
-        <v>6</v>
+        <v>5.909999847412109</v>
       </c>
       <c r="I26" t="n">
-        <v>4.166666666666666</v>
+        <v>4.230118552532127</v>
       </c>
       <c r="J26" t="n">
         <v>-21</v>
@@ -1745,10 +1745,10 @@
         </is>
       </c>
       <c r="H28" t="n">
-        <v>9.526000022888184</v>
+        <v>9.467000007629395</v>
       </c>
       <c r="I28" t="n">
-        <v>2.729372237825911</v>
+        <v>2.746382167428622</v>
       </c>
       <c r="J28" t="n">
         <v>-28</v>
@@ -1792,10 +1792,10 @@
         </is>
       </c>
       <c r="H29" t="n">
-        <v>13.80000019073486</v>
+        <v>13.60000038146973</v>
       </c>
       <c r="I29" t="n">
-        <v>4.347826026863623</v>
+        <v>4.411764582135689</v>
       </c>
       <c r="J29" t="n">
         <v>-28</v>
@@ -1839,10 +1839,10 @@
         </is>
       </c>
       <c r="H30" t="n">
-        <v>2.690000057220459</v>
+        <v>2.654000043869019</v>
       </c>
       <c r="I30" t="n">
-        <v>8.178438487742005</v>
+        <v>8.289374391994455</v>
       </c>
       <c r="J30" t="n">
         <v>-28</v>
@@ -1886,10 +1886,10 @@
         </is>
       </c>
       <c r="H31" t="n">
-        <v>0.4979999959468842</v>
+        <v>0.4659999907016754</v>
       </c>
       <c r="I31" t="n">
-        <v>0.8032128579428007</v>
+        <v>0.8583691158399027</v>
       </c>
       <c r="J31" t="n">
         <v>-28</v>
@@ -1933,10 +1933,10 @@
         </is>
       </c>
       <c r="H32" t="n">
-        <v>6.690000057220459</v>
+        <v>6.644999980926514</v>
       </c>
       <c r="I32" t="n">
-        <v>1.494768298126857</v>
+        <v>1.504890899729649</v>
       </c>
       <c r="J32" t="n">
         <v>-28</v>
@@ -3356,146 +3356,9 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C8"/>
+  <dimension ref="A1:A1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Stock</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>BEEWIZE</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Half Year Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>CALEFFI S.p.A.</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Half Year Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Industrie De Nora S.p.A.</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>MFE-MEDIAFOREUROPE N.V.</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>MFE-MEDIAFOREUROPE N.V.</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Half Year Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Pattern S.p.A.</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Half Year Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Somec S.p.A.</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Half Year Report</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
+  <sheetData/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>